--- a/Expenses.xlsx
+++ b/Expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PranavSheth\THYNK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A119E27F-FBB2-407C-B086-7CF35800E794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B615CC50-DFB2-4B9D-9D81-9E4CAAFAB351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38CDF89A-9897-480A-9E73-44E2162C06D9}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Investment</t>
   </si>
@@ -83,13 +83,19 @@
   </si>
   <si>
     <t>Workbook Printing</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>www.thynkedutech.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +111,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -114,7 +128,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -137,19 +151,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -462,13 +491,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE20B29-3E77-495E-A255-4E7575DCB4A7}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -578,7 +607,9 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>3322</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
         <v>15</v>
@@ -595,42 +626,63 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3322</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2">
-        <f>SUM(B3:B8)</f>
+      <c r="B11" s="2">
+        <f>SUM(B3:B10)</f>
         <v>11000</v>
       </c>
-      <c r="C9" s="2">
-        <f>SUM(C3:C8)</f>
-        <v>4925</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <f>SUM(F2:F8)</f>
-        <v>13925</v>
-      </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F10">
-        <f>F9/2</f>
-        <v>6962.5</v>
-      </c>
+      <c r="C11" s="2">
+        <f>SUM(C3:C10)</f>
+        <v>8247</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
+        <f>SUM(F2:F10)</f>
+        <v>17247</v>
+      </c>
+      <c r="G11" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:G1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{77147E26-0AED-458C-BFBB-7872CA16E09E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>